--- a/uomBirds.xlsx
+++ b/uomBirds.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git Projects\Mora-Bird-Diversity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6787EF-A7BD-473B-8040-1DEE936430A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1AC723-F20B-43E5-BC7A-CA7AA38CE5FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="637">
   <si>
     <t>Common Name</t>
   </si>
@@ -695,9 +695,6 @@
     <t>NT</t>
   </si>
   <si>
-    <t>Psittacidae</t>
-  </si>
-  <si>
     <t>Porphyrio poliocephalus</t>
   </si>
   <si>
@@ -857,9 +854,6 @@
     <t>Recurvirostridae</t>
   </si>
   <si>
-    <t>Observed in an exact single location located inside the Kaju kele multiple times.</t>
-  </si>
-  <si>
     <t>Open area behing the Boat yard and inside Kaju kele.</t>
   </si>
   <si>
@@ -1782,6 +1776,174 @@
   </si>
   <si>
     <t>Primarily feeds on insects like grasshoppers, caterpillars, dragonflies, and mantises. It also eats spiders, smaller insects, fruit, and nectar.</t>
+  </si>
+  <si>
+    <t>INDIAN PITTA</t>
+  </si>
+  <si>
+    <t>ORANGE-HEADED THRUSH</t>
+  </si>
+  <si>
+    <t>PIED CUCKOO</t>
+  </si>
+  <si>
+    <t>ALEXANDRINE PARAKEET</t>
+  </si>
+  <si>
+    <t>DARK-FRONTED BABBLER</t>
+  </si>
+  <si>
+    <t>LESSER YELLOWNAPE</t>
+  </si>
+  <si>
+    <t>LESSER WHITETHROAT</t>
+  </si>
+  <si>
+    <t>COMMON HAWK CUCKOO</t>
+  </si>
+  <si>
+    <t>PLAIN PRINIA</t>
+  </si>
+  <si>
+    <t>Hierococcyx varius</t>
+  </si>
+  <si>
+    <t>Clamator jacobinus</t>
+  </si>
+  <si>
+    <t>Pittidae</t>
+  </si>
+  <si>
+    <t>Pitta brachyura</t>
+  </si>
+  <si>
+    <t>Turdidae</t>
+  </si>
+  <si>
+    <t>Geokichla citrina</t>
+  </si>
+  <si>
+    <t>Psittaculidae</t>
+  </si>
+  <si>
+    <t>Psittacula eupatria</t>
+  </si>
+  <si>
+    <t>Timaliidae</t>
+  </si>
+  <si>
+    <t>Dumetia atriceps</t>
+  </si>
+  <si>
+    <t>Picus chlorolophus</t>
+  </si>
+  <si>
+    <t>Sylviidae</t>
+  </si>
+  <si>
+    <t>Curruca curruca</t>
+  </si>
+  <si>
+    <t>Prinia inornata</t>
+  </si>
+  <si>
+    <t>Jacobin Cuckoo</t>
+  </si>
+  <si>
+    <t>Observed in and around hotspot 2 over multiple seasons. Only one individual was present. It's primary host tree was cut down with the destruction of hotspot 2.</t>
+  </si>
+  <si>
+    <t>Single sighting of a pair at Kaju Kele.</t>
+  </si>
+  <si>
+    <t>Single sighting at Boat Yard.</t>
+  </si>
+  <si>
+    <t>Kaju kele around the hotspot 2.</t>
+  </si>
+  <si>
+    <t>Inside Kaju Kele and around the Department of Civil Engineering</t>
+  </si>
+  <si>
+    <t>Single sighting at Hotspot 2.</t>
+  </si>
+  <si>
+    <t>Near L Canteen, Sumanadasa, and inside Kaju Kele.</t>
+  </si>
+  <si>
+    <t>Boat Yard and Open area behing the Boat Yard.</t>
+  </si>
+  <si>
+    <t>Heard around Kaju Kele. Only one visual observation and was at the marsh near the new garbage dump site at hotspot 2.</t>
+  </si>
+  <si>
+    <t>Only a single individual. Several observations at the marshes near hotspot 2. Displayed pseudo nesting behaviour. Nest got destroyed by the fire set on garbage.</t>
+  </si>
+  <si>
+    <t>Common migrant except to the highest hills. Prefers undergrowth of forests.</t>
+  </si>
+  <si>
+    <t>Stout-billed, strong-legged bird with a buffy-and-black striped crown, black eye-stripe, green upperparts, blue shoulder patch, and a bright red vent.</t>
+  </si>
+  <si>
+    <t>While primarily insectivorous, also consumes Invertebrates and seeds.</t>
+  </si>
+  <si>
+    <t>Brightly colored ground-dwelling thrush with an unmistakable bright orange head, breast, and belly. Some subspecies also show two broad black crescents on the sides of the face.</t>
+  </si>
+  <si>
+    <t>Rare winter migrant to lowlands and lower hills. Prefers Forest,scrub and well wooded gardens with undercover.</t>
+  </si>
+  <si>
+    <t>a wide variety of invertebrates, such as earthworms, insects, spiders, snails, and leeches. It also consumes various berries, soft fruits, and fallen figs.</t>
+  </si>
+  <si>
+    <t>Uncommon breeding resident from lowlands to mid hills. A winter migrant population also exist.</t>
+  </si>
+  <si>
+    <t>Black-and-white crested cuckoo with glossy black upperparts, a white underbelly, and a bold white wing patch that stands out in flight and at rest.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Feeds on various insects, especially favoring hairy caterpillars. Also known for consuming some fruits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium-sized bird resembling Shikras' plumage. Males have ashy-gray upperparts, white underparts with rufous streaking and barring, a broadly barred tail, and a distinct yellow eye-ring. Females and juveniles are browner with heavier streaking below. </t>
+  </si>
+  <si>
+    <t>Uncommon breeding resident with a rare migrant population. Has become more regular on lowlands in the recent past. Highly arboreal.</t>
+  </si>
+  <si>
+    <t>Insectivores with special preference for catepillars.</t>
+  </si>
+  <si>
+    <t>Uncommon breeding resident found in lowlands up to lower hills. Forests and wooded areas are the preffered habitat.</t>
+  </si>
+  <si>
+    <t>Herbivorous and feeds on a variety of wild and cultivated seeds, buds, fruits, and nuts.</t>
+  </si>
+  <si>
+    <t>Uncommon breeding resident throughout Sri Lanka. Prefers dense undergrowth in forests.</t>
+  </si>
+  <si>
+    <t>Primarily insectivorous.</t>
+  </si>
+  <si>
+    <t>Uncommon breeding resident. Distributed from wet lowlands to adjacent drier areas. Forests and wooded areas are the preffered habitat.</t>
+  </si>
+  <si>
+    <t>insectivorous woodpecker. Diet consists primarily of ants, beetles, and their larvae. Also known to consume small fruits and nectar.</t>
+  </si>
+  <si>
+    <t>Rare winter migrant to dry lowlands. Prefers Scrubs.</t>
+  </si>
+  <si>
+    <t>primarily insectivorous carnivores, with a frugivorous component to their diet. They mainly feed on ants, flies, beetles, and other insects, while also consuming soft fruits.</t>
+  </si>
+  <si>
+    <t>Common breeding resident throughout the Island.Prefers paddyfields, scurb, marshes and reeds as habitat.</t>
+  </si>
+  <si>
+    <t>Diet consists almost entirely of small invertebrates, primarily ants, beetles, caterpillars, grasshoppers, spiders, and flies</t>
   </si>
 </sst>
 </file>
@@ -1800,23 +1962,27 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1845,7 +2011,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1912,6 +2078,12 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1966,7 +2138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2009,7 +2181,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2019,7 +2190,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2038,6 +2208,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2289,7 +2469,7 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="49" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -2333,8 +2513,8 @@
         <v>210</v>
       </c>
       <c r="E2" s="3"/>
-      <c r="F2" s="50" t="s">
-        <v>325</v>
+      <c r="F2" s="48" t="s">
+        <v>323</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>12</v>
@@ -2343,7 +2523,7 @@
         <v>13</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -2364,30 +2544,30 @@
       <c r="Z2" s="3"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>14</v>
+      <c r="A3" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="38" t="s">
-        <v>328</v>
+      <c r="F3" s="37" t="s">
+        <v>324</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>403</v>
+        <v>19</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>16</v>
+        <v>416</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -2408,30 +2588,30 @@
       <c r="Z3" s="3"/>
     </row>
     <row r="4" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>17</v>
+      <c r="A4" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E4" s="3"/>
-      <c r="F4" s="38" t="s">
+      <c r="F4" s="37" t="s">
         <v>326</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>19</v>
+        <v>401</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>418</v>
+        <v>16</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -2453,7 +2633,7 @@
     </row>
     <row r="5" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>20</v>
@@ -2465,11 +2645,11 @@
         <v>210</v>
       </c>
       <c r="E5" s="3"/>
-      <c r="F5" s="38" t="s">
-        <v>547</v>
+      <c r="F5" s="37" t="s">
+        <v>545</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>21</v>
@@ -2497,31 +2677,31 @@
     </row>
     <row r="6" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B6" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" s="28" t="s">
         <v>269</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>270</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>210</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -2543,29 +2723,29 @@
     </row>
     <row r="7" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>484</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="D7" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="E7" s="35"/>
+      <c r="F7" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="D7" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="E7" s="36"/>
-      <c r="F7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>489</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>491</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -2587,29 +2767,29 @@
     </row>
     <row r="8" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="B8" s="52" t="s">
+        <v>575</v>
+      </c>
+      <c r="C8" s="51" t="s">
         <v>576</v>
-      </c>
-      <c r="B8" s="54" t="s">
-        <v>577</v>
-      </c>
-      <c r="C8" s="53" t="s">
-        <v>578</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>210</v>
       </c>
       <c r="E8" s="29"/>
-      <c r="F8" s="46" t="s">
+      <c r="F8" s="44" t="s">
+        <v>577</v>
+      </c>
+      <c r="G8" s="44" t="s">
+        <v>578</v>
+      </c>
+      <c r="H8" s="44" t="s">
         <v>579</v>
       </c>
-      <c r="G8" s="46" t="s">
+      <c r="I8" s="44" t="s">
         <v>580</v>
-      </c>
-      <c r="H8" s="46" t="s">
-        <v>581</v>
-      </c>
-      <c r="I8" s="46" t="s">
-        <v>582</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -2629,12 +2809,12 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
     </row>
-    <row r="9" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>23</v>
+    <row r="9" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>24</v>
@@ -2643,17 +2823,17 @@
         <v>210</v>
       </c>
       <c r="E9" s="3"/>
-      <c r="F9" s="39" t="s">
-        <v>548</v>
+      <c r="F9" s="18" t="s">
+        <v>546</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>368</v>
+        <v>517</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>404</v>
+        <v>30</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>25</v>
+        <v>423</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -2675,10 +2855,10 @@
     </row>
     <row r="10" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>24</v>
@@ -2686,20 +2866,18 @@
       <c r="D10" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="F10" s="39" t="s">
-        <v>329</v>
+      <c r="E10" s="28"/>
+      <c r="F10" s="38" t="s">
+        <v>546</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>369</v>
+        <v>516</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -2721,10 +2899,10 @@
     </row>
     <row r="11" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>298</v>
+        <v>223</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>24</v>
@@ -2732,18 +2910,18 @@
       <c r="D11" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="E11" s="28"/>
-      <c r="F11" s="39" t="s">
-        <v>548</v>
+      <c r="E11" s="3"/>
+      <c r="F11" s="38" t="s">
+        <v>546</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>518</v>
+        <v>366</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>424</v>
+        <v>25</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -2763,12 +2941,12 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
     </row>
-    <row r="12" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>29</v>
+    <row r="12" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>26</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>24</v>
@@ -2776,18 +2954,20 @@
       <c r="D12" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="18" t="s">
-        <v>548</v>
-      </c>
-      <c r="G12" s="29" t="s">
-        <v>519</v>
+      <c r="E12" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>327</v>
+      </c>
+      <c r="G12" s="64" t="s">
+        <v>367</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>30</v>
+        <v>403</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -2809,7 +2989,7 @@
     </row>
     <row r="13" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>31</v>
@@ -2821,14 +3001,14 @@
         <v>210</v>
       </c>
       <c r="E13" s="3"/>
-      <c r="F13" s="38" t="s">
-        <v>548</v>
-      </c>
-      <c r="G13" s="56" t="s">
-        <v>370</v>
+      <c r="F13" s="37" t="s">
+        <v>546</v>
+      </c>
+      <c r="G13" s="54" t="s">
+        <v>368</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>33</v>
@@ -2865,14 +3045,14 @@
         <v>210</v>
       </c>
       <c r="E14" s="3"/>
-      <c r="F14" s="38" t="s">
-        <v>548</v>
+      <c r="F14" s="37" t="s">
+        <v>546</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>37</v>
@@ -2897,7 +3077,7 @@
     </row>
     <row r="15" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>38</v>
@@ -2909,17 +3089,17 @@
         <v>210</v>
       </c>
       <c r="E15" s="3"/>
-      <c r="F15" s="38" t="s">
-        <v>330</v>
+      <c r="F15" s="37" t="s">
+        <v>328</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -2953,17 +3133,17 @@
         <v>209</v>
       </c>
       <c r="E16" s="3"/>
-      <c r="F16" s="39" t="s">
-        <v>331</v>
+      <c r="F16" s="38" t="s">
+        <v>329</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -2985,10 +3165,10 @@
     </row>
     <row r="17" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>39</v>
@@ -2997,19 +3177,19 @@
         <v>210</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>572</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>574</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
@@ -3029,33 +3209,31 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
     </row>
-    <row r="18" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="3" t="s">
+    <row r="18" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>554</v>
+      </c>
+      <c r="C18" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="F18" s="38" t="s">
-        <v>548</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>372</v>
+      <c r="E18" s="3"/>
+      <c r="F18" s="18" t="s">
+        <v>556</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>558</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>46</v>
+        <v>557</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>47</v>
+        <v>559</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
@@ -3077,10 +3255,10 @@
     </row>
     <row r="19" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>48</v>
+        <v>300</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>45</v>
@@ -3089,17 +3267,17 @@
         <v>210</v>
       </c>
       <c r="E19" s="3"/>
-      <c r="F19" s="7" t="s">
-        <v>548</v>
+      <c r="F19" s="5" t="s">
+        <v>546</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>373</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
@@ -3119,31 +3297,33 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
     </row>
-    <row r="20" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>52</v>
+    <row r="20" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>288</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="5" t="s">
-        <v>548</v>
+      <c r="E20" s="35" t="s">
+        <v>475</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>290</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>374</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>53</v>
+        <v>291</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>443</v>
+        <v>470</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
@@ -3163,12 +3343,12 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>54</v>
+    <row r="21" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>57</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>45</v>
@@ -3177,17 +3357,17 @@
         <v>210</v>
       </c>
       <c r="E21" s="3"/>
-      <c r="F21" s="5" t="s">
-        <v>548</v>
+      <c r="F21" s="3" t="s">
+        <v>547</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>375</v>
+        <v>513</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>56</v>
+        <v>471</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
@@ -3209,29 +3389,29 @@
     </row>
     <row r="22" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>516</v>
+        <v>495</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>57</v>
+        <v>496</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="13" t="s">
         <v>210</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>515</v>
+        <v>552</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>58</v>
+        <v>497</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>473</v>
+        <v>498</v>
       </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
@@ -3251,31 +3431,31 @@
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
     </row>
-    <row r="23" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="B23" s="24" t="s">
-        <v>271</v>
-      </c>
-      <c r="C23" s="28" t="s">
+    <row r="23" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="19" t="s">
         <v>210</v>
       </c>
       <c r="E23" s="3"/>
-      <c r="F23" s="3" t="s">
-        <v>276</v>
+      <c r="F23" s="5" t="s">
+        <v>546</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>521</v>
+        <v>372</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>285</v>
+        <v>53</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
@@ -3295,33 +3475,33 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
     </row>
-    <row r="24" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>290</v>
+    <row r="24" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>44</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="E24" s="36" t="s">
-        <v>477</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>292</v>
+      <c r="E24" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="F24" s="37" t="s">
+        <v>546</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>293</v>
+        <v>46</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>472</v>
+        <v>47</v>
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
@@ -3343,10 +3523,10 @@
     </row>
     <row r="25" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="B25" s="17" t="s">
         <v>289</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>291</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>45</v>
@@ -3356,16 +3536,16 @@
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
@@ -3385,31 +3565,31 @@
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
     </row>
-    <row r="26" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>493</v>
+    <row r="26" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D26" s="13" t="s">
-        <v>494</v>
+      <c r="D26" s="19" t="s">
+        <v>210</v>
       </c>
       <c r="E26" s="3"/>
-      <c r="F26" s="3" t="s">
-        <v>548</v>
+      <c r="F26" s="7" t="s">
+        <v>546</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>544</v>
+        <v>371</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>495</v>
+        <v>50</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>496</v>
+        <v>51</v>
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
@@ -3431,12 +3611,12 @@
     </row>
     <row r="27" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>498</v>
-      </c>
-      <c r="C27" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="C27" s="28" t="s">
         <v>45</v>
       </c>
       <c r="D27" s="13" t="s">
@@ -3444,16 +3624,16 @@
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>548</v>
+        <v>274</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>554</v>
+        <v>519</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>499</v>
+        <v>283</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>500</v>
+        <v>417</v>
       </c>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
@@ -3475,29 +3655,29 @@
     </row>
     <row r="28" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>555</v>
-      </c>
-      <c r="B28" s="24" t="s">
-        <v>556</v>
-      </c>
-      <c r="C28" s="18" t="s">
+        <v>490</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>210</v>
+        <v>492</v>
       </c>
       <c r="E28" s="3"/>
-      <c r="F28" s="18" t="s">
-        <v>558</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>560</v>
+      <c r="F28" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>542</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>559</v>
+        <v>493</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>561</v>
+        <v>494</v>
       </c>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
@@ -3519,29 +3699,29 @@
     </row>
     <row r="29" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="C29" s="28" t="s">
         <v>255</v>
-      </c>
-      <c r="B29" s="24" t="s">
-        <v>254</v>
-      </c>
-      <c r="C29" s="28" t="s">
-        <v>256</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>210</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="18" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
@@ -3563,7 +3743,7 @@
     </row>
     <row r="30" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B30" s="16" t="s">
         <v>59</v>
@@ -3575,14 +3755,14 @@
         <v>210</v>
       </c>
       <c r="E30" s="3"/>
-      <c r="F30" s="55" t="s">
-        <v>242</v>
+      <c r="F30" s="53" t="s">
+        <v>241</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>61</v>
@@ -3606,30 +3786,30 @@
       <c r="Z30" s="3"/>
     </row>
     <row r="31" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A31" s="40" t="s">
+      <c r="A31" s="39" t="s">
+        <v>260</v>
+      </c>
+      <c r="B31" s="24" t="s">
         <v>261</v>
       </c>
-      <c r="B31" s="24" t="s">
+      <c r="C31" s="28" t="s">
         <v>262</v>
-      </c>
-      <c r="C31" s="28" t="s">
-        <v>263</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>210</v>
       </c>
       <c r="E31" s="3"/>
-      <c r="F31" s="46" t="s">
-        <v>333</v>
+      <c r="F31" s="44" t="s">
+        <v>331</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
@@ -3664,16 +3844,16 @@
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="29" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
@@ -3708,16 +3888,16 @@
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
@@ -3752,16 +3932,16 @@
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
@@ -3781,31 +3961,29 @@
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
     </row>
-    <row r="35" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A35" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>71</v>
+    <row r="35" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A35" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="B35" s="29" t="s">
+        <v>603</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D35" s="19" t="s">
-        <v>294</v>
+        <v>69</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>210</v>
       </c>
       <c r="E35" s="3"/>
-      <c r="F35" s="5" t="s">
-        <v>73</v>
+      <c r="F35" s="3" t="s">
+        <v>612</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>74</v>
-      </c>
+        <v>635</v>
+      </c>
+      <c r="H35" s="56"/>
       <c r="I35" s="3" t="s">
-        <v>75</v>
+        <v>636</v>
       </c>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
@@ -3839,11 +4017,11 @@
         <v>210</v>
       </c>
       <c r="E36" s="3"/>
-      <c r="F36" s="38" t="s">
-        <v>334</v>
+      <c r="F36" s="37" t="s">
+        <v>332</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>78</v>
@@ -3870,30 +4048,30 @@
       <c r="Z36" s="3"/>
     </row>
     <row r="37" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>212</v>
+      <c r="A37" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>71</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>210</v>
+        <v>292</v>
       </c>
       <c r="E37" s="3"/>
-      <c r="F37" s="38" t="s">
-        <v>335</v>
+      <c r="F37" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>524</v>
+        <v>377</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
@@ -3913,31 +4091,31 @@
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
     </row>
-    <row r="38" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A38" s="30" t="s">
-        <v>247</v>
-      </c>
-      <c r="B38" s="31" t="s">
-        <v>259</v>
-      </c>
-      <c r="C38" s="32" t="s">
+    <row r="38" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A38" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D38" s="33" t="s">
+      <c r="D38" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="E38" s="33"/>
-      <c r="F38" s="33" t="s">
-        <v>338</v>
-      </c>
-      <c r="G38" s="33" t="s">
-        <v>525</v>
-      </c>
-      <c r="H38" s="33" t="s">
-        <v>278</v>
-      </c>
-      <c r="I38" s="33" t="s">
-        <v>428</v>
+      <c r="E38" s="3"/>
+      <c r="F38" s="37" t="s">
+        <v>333</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
@@ -3957,31 +4135,31 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
-    <row r="39" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B39" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D39" s="19" t="s">
+    <row r="39" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A39" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="C39" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="D39" s="33" t="s">
         <v>210</v>
       </c>
-      <c r="E39" s="3"/>
-      <c r="F39" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>429</v>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33" t="s">
+        <v>336</v>
+      </c>
+      <c r="G39" s="33" t="s">
+        <v>523</v>
+      </c>
+      <c r="H39" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="I39" s="33" t="s">
+        <v>426</v>
       </c>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
@@ -4003,10 +4181,10 @@
     </row>
     <row r="40" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>85</v>
@@ -4014,20 +4192,18 @@
       <c r="D40" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="F40" s="38" t="s">
-        <v>336</v>
+      <c r="E40" s="3"/>
+      <c r="F40" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
@@ -4048,32 +4224,32 @@
       <c r="Z40" s="3"/>
     </row>
     <row r="41" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="11" t="s">
-        <v>91</v>
+      <c r="A41" s="8" t="s">
+        <v>88</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D41" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="E41" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="F41" s="38" t="s">
-        <v>339</v>
+      <c r="E41" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F41" s="37" t="s">
+        <v>334</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>526</v>
+        <v>393</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
@@ -4094,11 +4270,11 @@
       <c r="Z41" s="3"/>
     </row>
     <row r="42" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A42" s="8" t="s">
-        <v>305</v>
+      <c r="A42" s="11" t="s">
+        <v>91</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>93</v>
@@ -4106,20 +4282,20 @@
       <c r="D42" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>340</v>
+      <c r="E42" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="F42" s="37" t="s">
+        <v>337</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>382</v>
+        <v>524</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
@@ -4139,31 +4315,31 @@
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
     </row>
-    <row r="43" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A43" s="40" t="s">
-        <v>501</v>
-      </c>
-      <c r="B43" s="21" t="s">
-        <v>502</v>
+    <row r="43" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="B43" s="29" t="s">
+        <v>590</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D43" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="E43" s="36"/>
+      <c r="D43" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E43" s="3"/>
       <c r="F43" s="3" t="s">
-        <v>503</v>
+        <v>611</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>527</v>
+        <v>625</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>504</v>
+        <v>624</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>505</v>
+        <v>626</v>
       </c>
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
@@ -4184,30 +4360,30 @@
       <c r="Z43" s="3"/>
     </row>
     <row r="44" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A44" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="B44" s="16" t="s">
-        <v>97</v>
+      <c r="A44" s="39" t="s">
+        <v>499</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>500</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D44" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="E44" s="3"/>
-      <c r="F44" s="5" t="s">
-        <v>337</v>
+        <v>93</v>
+      </c>
+      <c r="D44" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="E44" s="35"/>
+      <c r="F44" s="3" t="s">
+        <v>501</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>396</v>
+        <v>525</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>99</v>
+        <v>502</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>434</v>
+        <v>503</v>
       </c>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
@@ -4229,29 +4405,31 @@
     </row>
     <row r="45" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
-        <v>228</v>
+        <v>303</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D45" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="E45" s="3"/>
+      <c r="E45" s="3" t="s">
+        <v>304</v>
+      </c>
       <c r="F45" s="5" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>102</v>
+        <v>380</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
@@ -4273,29 +4451,31 @@
     </row>
     <row r="46" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="B46" s="17" t="s">
-        <v>104</v>
+        <v>583</v>
+      </c>
+      <c r="B46" s="29" t="s">
+        <v>591</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D46" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E46" s="3"/>
+      <c r="E46" s="3" t="s">
+        <v>604</v>
+      </c>
       <c r="F46" s="3" t="s">
-        <v>342</v>
+        <v>607</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>528</v>
+        <v>621</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>106</v>
+        <v>622</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>436</v>
+        <v>623</v>
       </c>
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
@@ -4315,31 +4495,31 @@
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
     </row>
-    <row r="47" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="B47" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="C47" s="28" t="s">
-        <v>105</v>
-      </c>
-      <c r="D47" s="13" t="s">
+    <row r="47" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A47" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D47" s="19" t="s">
         <v>210</v>
       </c>
       <c r="E47" s="3"/>
-      <c r="F47" s="3" t="s">
-        <v>343</v>
+      <c r="F47" s="5" t="s">
+        <v>335</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>529</v>
+        <v>394</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>279</v>
+        <v>99</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
@@ -4361,29 +4541,29 @@
     </row>
     <row r="48" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="B48" s="21" t="s">
-        <v>108</v>
+        <v>227</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>100</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D48" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="E48" s="36"/>
+        <v>101</v>
+      </c>
+      <c r="D48" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="E48" s="3"/>
       <c r="F48" s="5" t="s">
-        <v>244</v>
+        <v>339</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>383</v>
+        <v>102</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
@@ -4403,31 +4583,31 @@
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
     </row>
-    <row r="49" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A49" s="11" t="s">
-        <v>307</v>
-      </c>
-      <c r="B49" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>109</v>
+    <row r="49" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A49" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B49" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="D49" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="E49" s="12"/>
-      <c r="F49" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="G49" s="12" t="s">
-        <v>530</v>
-      </c>
-      <c r="H49" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="I49" s="12" t="s">
-        <v>439</v>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>434</v>
       </c>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
@@ -4449,29 +4629,29 @@
     </row>
     <row r="50" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="B50" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D50" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="B50" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="C50" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D50" s="13" t="s">
         <v>210</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3" t="s">
-        <v>241</v>
+        <v>341</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>384</v>
+        <v>527</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>115</v>
+        <v>277</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
@@ -4491,31 +4671,31 @@
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
     </row>
-    <row r="51" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A51" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="B51" s="25" t="s">
-        <v>257</v>
-      </c>
-      <c r="C51" s="28" t="s">
-        <v>258</v>
+    <row r="51" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A51" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>109</v>
       </c>
       <c r="D51" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="E51" s="49"/>
-      <c r="F51" s="3" t="s">
-        <v>274</v>
+        <v>221</v>
+      </c>
+      <c r="E51" s="47"/>
+      <c r="F51" s="5" t="s">
+        <v>243</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>277</v>
+        <v>110</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
@@ -4536,30 +4716,30 @@
       <c r="Z51" s="3"/>
     </row>
     <row r="52" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A52" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="B52" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D52" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="E52" s="36"/>
+      <c r="A52" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="E52" s="12"/>
       <c r="F52" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>442</v>
+        <v>244</v>
+      </c>
+      <c r="G52" s="12" t="s">
+        <v>528</v>
+      </c>
+      <c r="H52" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="I52" s="12" t="s">
+        <v>437</v>
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
@@ -4580,30 +4760,30 @@
       <c r="Z52" s="3"/>
     </row>
     <row r="53" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A53" s="40" t="s">
-        <v>249</v>
-      </c>
-      <c r="B53" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="C53" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="D53" s="13" t="s">
-        <v>209</v>
+      <c r="A53" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B53" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D53" s="19" t="s">
+        <v>210</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3" t="s">
-        <v>357</v>
+        <v>240</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>281</v>
+        <v>115</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
@@ -4623,31 +4803,31 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
-    <row r="54" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A54" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="B54" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="C54" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="D54" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="E54" s="3"/>
-      <c r="F54" s="5" t="s">
-        <v>344</v>
+    <row r="54" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A54" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="B54" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="C54" s="28" t="s">
+        <v>257</v>
+      </c>
+      <c r="D54" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="E54" s="35"/>
+      <c r="F54" s="3" t="s">
+        <v>605</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>121</v>
+        <v>383</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>122</v>
+        <v>275</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
@@ -4667,31 +4847,31 @@
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
     </row>
-    <row r="55" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A55" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="B55" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D55" s="19" t="s">
-        <v>210</v>
+    <row r="55" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A55" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="B55" s="62" t="s">
+        <v>263</v>
+      </c>
+      <c r="C55" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>209</v>
       </c>
       <c r="E55" s="3"/>
-      <c r="F55" s="5" t="s">
-        <v>345</v>
+      <c r="F55" s="3" t="s">
+        <v>355</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>124</v>
+        <v>395</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>125</v>
+        <v>279</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>470</v>
+        <v>442</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
@@ -4712,32 +4892,30 @@
       <c r="Z55" s="3"/>
     </row>
     <row r="56" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A56" s="35" t="s">
-        <v>309</v>
-      </c>
-      <c r="B56" s="44" t="s">
-        <v>216</v>
-      </c>
-      <c r="C56" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="D56" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="E56" s="12" t="s">
-        <v>310</v>
-      </c>
+      <c r="A56" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B56" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D56" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="E56" s="35"/>
       <c r="F56" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="G56" s="12" t="s">
-        <v>532</v>
-      </c>
-      <c r="H56" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="I56" s="12" t="s">
-        <v>127</v>
+        <v>240</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>440</v>
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
@@ -4759,29 +4937,29 @@
     </row>
     <row r="57" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="B57" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>129</v>
+        <v>306</v>
+      </c>
+      <c r="B57" s="42" t="s">
+        <v>214</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>120</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="E57" s="36"/>
+        <v>210</v>
+      </c>
+      <c r="E57" s="3"/>
       <c r="F57" s="5" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>533</v>
+        <v>121</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
@@ -4803,31 +4981,29 @@
     </row>
     <row r="58" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B58" s="14" t="s">
-        <v>132</v>
+        <v>230</v>
+      </c>
+      <c r="B58" s="42" t="s">
+        <v>215</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D58" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="E58" s="4" t="s">
-        <v>312</v>
-      </c>
+      <c r="E58" s="3"/>
       <c r="F58" s="5" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>393</v>
+        <v>124</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
@@ -4848,30 +5024,32 @@
       <c r="Z58" s="3"/>
     </row>
     <row r="59" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A59" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B59" s="45" t="s">
-        <v>313</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D59" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="E59" s="36"/>
+      <c r="A59" s="34" t="s">
+        <v>307</v>
+      </c>
+      <c r="B59" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D59" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>308</v>
+      </c>
       <c r="F59" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>448</v>
+        <v>344</v>
+      </c>
+      <c r="G59" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="H59" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="I59" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="J59" s="3"/>
       <c r="K59" s="3"/>
@@ -4893,29 +5071,29 @@
     </row>
     <row r="60" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="B60" s="45" t="s">
-        <v>479</v>
+        <v>309</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>128</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D60" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="E60" s="36"/>
+        <v>129</v>
+      </c>
+      <c r="D60" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="E60" s="35"/>
       <c r="F60" s="5" t="s">
-        <v>480</v>
+        <v>345</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>484</v>
+        <v>531</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>481</v>
+        <v>130</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>482</v>
+        <v>444</v>
       </c>
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
@@ -4937,29 +5115,31 @@
     </row>
     <row r="61" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D61" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="E61" s="3"/>
+      <c r="E61" s="4" t="s">
+        <v>310</v>
+      </c>
       <c r="F61" s="5" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>534</v>
+        <v>391</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="J61" s="3"/>
       <c r="K61" s="3"/>
@@ -4980,30 +5160,30 @@
       <c r="Z61" s="3"/>
     </row>
     <row r="62" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A62" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="B62" s="44" t="s">
-        <v>142</v>
+      <c r="A62" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B62" s="43" t="s">
+        <v>311</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D62" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="E62" s="3"/>
-      <c r="F62" s="23" t="s">
-        <v>351</v>
+        <v>136</v>
+      </c>
+      <c r="D62" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="E62" s="35"/>
+      <c r="F62" s="5" t="s">
+        <v>347</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>535</v>
+        <v>137</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I62" s="29" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
@@ -5024,30 +5204,30 @@
       <c r="Z62" s="3"/>
     </row>
     <row r="63" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A63" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="B63" s="27" t="s">
-        <v>145</v>
+      <c r="A63" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B63" s="43" t="s">
+        <v>477</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D63" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="E63" s="36"/>
+        <v>221</v>
+      </c>
+      <c r="E63" s="35"/>
       <c r="F63" s="5" t="s">
-        <v>146</v>
+        <v>478</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>147</v>
+        <v>482</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>148</v>
+        <v>479</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
@@ -5067,31 +5247,31 @@
       <c r="Y63" s="3"/>
       <c r="Z63" s="3"/>
     </row>
-    <row r="64" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B64" s="13" t="s">
-        <v>218</v>
+    <row r="64" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>140</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D64" s="19" t="s">
         <v>210</v>
       </c>
       <c r="E64" s="3"/>
-      <c r="F64" s="3" t="s">
-        <v>352</v>
+      <c r="F64" s="5" t="s">
+        <v>348</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>386</v>
+        <v>532</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
@@ -5112,30 +5292,30 @@
       <c r="Z64" s="3"/>
     </row>
     <row r="65" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A65" s="48" t="s">
-        <v>250</v>
+      <c r="A65" s="46" t="s">
+        <v>249</v>
       </c>
       <c r="B65" s="25" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C65" t="s">
         <v>143</v>
       </c>
       <c r="D65" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="E65" s="36"/>
+        <v>221</v>
+      </c>
+      <c r="E65" s="35"/>
       <c r="F65" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J65" s="3"/>
       <c r="K65" s="3"/>
@@ -5156,30 +5336,30 @@
       <c r="Z65" s="3"/>
     </row>
     <row r="66" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A66" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="B66" s="16" t="s">
-        <v>150</v>
+      <c r="A66" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="B66" s="21" t="s">
+        <v>145</v>
       </c>
       <c r="C66" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="D66" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="E66" s="3"/>
+        <v>143</v>
+      </c>
+      <c r="D66" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="E66" s="35"/>
       <c r="F66" s="5" t="s">
-        <v>353</v>
+        <v>146</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>387</v>
+        <v>147</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
@@ -5199,33 +5379,31 @@
       <c r="Y66" s="3"/>
       <c r="Z66" s="3"/>
     </row>
-    <row r="67" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A67" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="B67" s="16" t="s">
-        <v>153</v>
+    <row r="67" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B67" s="17" t="s">
+        <v>218</v>
       </c>
       <c r="C67" s="29" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D67" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="E67" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>354</v>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3" t="s">
+        <v>350</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
@@ -5246,30 +5424,30 @@
       <c r="Z67" s="3"/>
     </row>
     <row r="68" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A68" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="B68" s="21" t="s">
-        <v>156</v>
+      <c r="A68" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="B68" s="20" t="s">
+        <v>142</v>
       </c>
       <c r="C68" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="D68" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="E68" s="36"/>
-      <c r="F68" s="5" t="s">
-        <v>355</v>
+        <v>143</v>
+      </c>
+      <c r="D68" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="E68" s="3"/>
+      <c r="F68" s="23" t="s">
+        <v>349</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>158</v>
+        <v>533</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
@@ -5291,29 +5469,31 @@
     </row>
     <row r="69" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>234</v>
+        <v>313</v>
       </c>
       <c r="B69" s="16" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C69" s="29" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D69" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="E69" s="3"/>
+      <c r="E69" s="3" t="s">
+        <v>314</v>
+      </c>
       <c r="F69" s="5" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
@@ -5333,31 +5513,31 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="3"/>
     </row>
-    <row r="70" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="B70" s="17" t="s">
-        <v>162</v>
+    <row r="70" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A70" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B70" s="16" t="s">
+        <v>150</v>
       </c>
       <c r="C70" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="D70" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="D70" s="19" t="s">
         <v>210</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="5" t="s">
-        <v>549</v>
+        <v>351</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="J70" s="3"/>
       <c r="K70" s="3"/>
@@ -5377,31 +5557,31 @@
       <c r="Y70" s="3"/>
       <c r="Z70" s="3"/>
     </row>
-    <row r="71" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B71" s="17" t="s">
-        <v>165</v>
+    <row r="71" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A71" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B71" s="16" t="s">
+        <v>160</v>
       </c>
       <c r="C71" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="D71" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="D71" s="19" t="s">
         <v>210</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="5" t="s">
-        <v>548</v>
+        <v>354</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>537</v>
+        <v>386</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>169</v>
+        <v>453</v>
       </c>
       <c r="J71" s="3"/>
       <c r="K71" s="3"/>
@@ -5421,31 +5601,31 @@
       <c r="Y71" s="3"/>
       <c r="Z71" s="3"/>
     </row>
-    <row r="72" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A72" s="43" t="s">
-        <v>170</v>
-      </c>
-      <c r="B72" s="17" t="s">
-        <v>171</v>
+    <row r="72" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A72" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B72" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="C72" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="D72" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="E72" s="3"/>
+        <v>157</v>
+      </c>
+      <c r="D72" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="E72" s="35"/>
       <c r="F72" s="5" t="s">
-        <v>548</v>
+        <v>353</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>390</v>
+        <v>158</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>173</v>
+        <v>454</v>
       </c>
       <c r="J72" s="3"/>
       <c r="K72" s="3"/>
@@ -5467,29 +5647,29 @@
     </row>
     <row r="73" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>174</v>
+        <v>234</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="C73" s="29" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D73" s="13" t="s">
         <v>210</v>
       </c>
       <c r="E73" s="3"/>
-      <c r="F73" s="3" t="s">
-        <v>548</v>
+      <c r="F73" s="5" t="s">
+        <v>547</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>538</v>
+        <v>387</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
       <c r="J73" s="3"/>
       <c r="K73" s="3"/>
@@ -5511,29 +5691,29 @@
     </row>
     <row r="74" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A74" s="41" t="s">
-        <v>562</v>
-      </c>
-      <c r="B74" s="24" t="s">
-        <v>564</v>
-      </c>
-      <c r="C74" t="s">
-        <v>565</v>
+        <v>170</v>
+      </c>
+      <c r="B74" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="C74" s="29" t="s">
+        <v>166</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="E74" s="3"/>
-      <c r="F74" s="3" t="s">
-        <v>568</v>
+      <c r="F74" s="5" t="s">
+        <v>546</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>569</v>
+        <v>388</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>570</v>
+        <v>172</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>571</v>
+        <v>173</v>
       </c>
       <c r="J74" s="3"/>
       <c r="K74" s="3"/>
@@ -5553,31 +5733,31 @@
       <c r="Y74" s="3"/>
       <c r="Z74" s="3"/>
     </row>
-    <row r="75" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A75" s="47" t="s">
-        <v>317</v>
-      </c>
-      <c r="B75" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="C75" s="34" t="s">
-        <v>178</v>
+    <row r="75" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B75" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="C75" s="29" t="s">
+        <v>166</v>
       </c>
       <c r="D75" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="E75" s="12"/>
+      <c r="E75" s="3"/>
       <c r="F75" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="G75" s="12" t="s">
-        <v>391</v>
-      </c>
-      <c r="H75" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="I75" s="12" t="s">
-        <v>459</v>
+        <v>546</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>169</v>
       </c>
       <c r="J75" s="3"/>
       <c r="K75" s="3"/>
@@ -5597,31 +5777,31 @@
       <c r="Y75" s="3"/>
       <c r="Z75" s="3"/>
     </row>
-    <row r="76" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A76" s="35" t="s">
-        <v>318</v>
-      </c>
-      <c r="B76" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="C76" s="34" t="s">
-        <v>220</v>
+    <row r="76" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B76" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="C76" s="29" t="s">
+        <v>166</v>
       </c>
       <c r="D76" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="E76" s="12"/>
-      <c r="F76" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="G76" s="12" t="s">
-        <v>399</v>
-      </c>
-      <c r="H76" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="I76" s="12" t="s">
-        <v>460</v>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>474</v>
       </c>
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
@@ -5641,31 +5821,31 @@
       <c r="Y76" s="3"/>
       <c r="Z76" s="3"/>
     </row>
-    <row r="77" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A77" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="B77" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>220</v>
+    <row r="77" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A77" s="40" t="s">
+        <v>560</v>
+      </c>
+      <c r="B77" s="26" t="s">
+        <v>562</v>
+      </c>
+      <c r="C77" s="28" t="s">
+        <v>563</v>
       </c>
       <c r="D77" s="13" t="s">
         <v>210</v>
       </c>
       <c r="E77" s="3"/>
-      <c r="F77" s="5" t="s">
-        <v>360</v>
+      <c r="F77" s="3" t="s">
+        <v>566</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>539</v>
+        <v>567</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>183</v>
+        <v>568</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>461</v>
+        <v>569</v>
       </c>
       <c r="J77" s="3"/>
       <c r="K77" s="3"/>
@@ -5685,31 +5865,29 @@
       <c r="Y77" s="3"/>
       <c r="Z77" s="3"/>
     </row>
-    <row r="78" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A78" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B78" s="14" t="s">
-        <v>184</v>
+    <row r="78" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>600</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D78" s="13" t="s">
-        <v>210</v>
+        <v>178</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>219</v>
       </c>
       <c r="E78" s="3"/>
-      <c r="F78" s="5" t="s">
-        <v>356</v>
+      <c r="F78" s="3" t="s">
+        <v>609</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>187</v>
-      </c>
+        <v>631</v>
+      </c>
+      <c r="H78" s="56"/>
       <c r="I78" s="3" t="s">
-        <v>462</v>
+        <v>632</v>
       </c>
       <c r="J78" s="3"/>
       <c r="K78" s="3"/>
@@ -5729,31 +5907,31 @@
       <c r="Y78" s="3"/>
       <c r="Z78" s="3"/>
     </row>
-    <row r="79" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="B79" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>185</v>
+    <row r="79" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A79" s="45" t="s">
+        <v>315</v>
+      </c>
+      <c r="B79" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>178</v>
       </c>
       <c r="D79" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="E79" s="3"/>
-      <c r="F79" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>463</v>
+      <c r="E79" s="12"/>
+      <c r="F79" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="G79" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="H79" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="I79" s="12" t="s">
+        <v>457</v>
       </c>
       <c r="J79" s="3"/>
       <c r="K79" s="3"/>
@@ -5773,31 +5951,31 @@
       <c r="Y79" s="3"/>
       <c r="Z79" s="3"/>
     </row>
-    <row r="80" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A80" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="B80" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="C80" s="29" t="s">
-        <v>191</v>
-      </c>
-      <c r="D80" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="E80" s="29"/>
-      <c r="F80" s="55" t="s">
-        <v>552</v>
-      </c>
-      <c r="G80" s="29" t="s">
-        <v>541</v>
-      </c>
-      <c r="H80" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="I80" s="29" t="s">
-        <v>193</v>
+    <row r="80" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A80" s="58" t="s">
+        <v>581</v>
+      </c>
+      <c r="B80" s="59" t="s">
+        <v>593</v>
+      </c>
+      <c r="C80" s="59" t="s">
+        <v>592</v>
+      </c>
+      <c r="D80" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="E80" s="59"/>
+      <c r="F80" s="59" t="s">
+        <v>613</v>
+      </c>
+      <c r="G80" s="59" t="s">
+        <v>615</v>
+      </c>
+      <c r="H80" s="59" t="s">
+        <v>616</v>
+      </c>
+      <c r="I80" s="59" t="s">
+        <v>617</v>
       </c>
       <c r="J80" s="3"/>
       <c r="K80" s="3"/>
@@ -5817,33 +5995,29 @@
       <c r="Y80" s="3"/>
       <c r="Z80" s="3"/>
     </row>
-    <row r="81" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A81" s="42" t="s">
-        <v>320</v>
-      </c>
-      <c r="B81" s="16" t="s">
-        <v>221</v>
+    <row r="81" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A81" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="B81" s="29" t="s">
+        <v>597</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D81" s="13" t="s">
+        <v>596</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E81" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>553</v>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3" t="s">
+        <v>608</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>194</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="H81" s="56"/>
       <c r="I81" s="3" t="s">
-        <v>464</v>
+        <v>628</v>
       </c>
       <c r="J81" s="3"/>
       <c r="K81" s="3"/>
@@ -5863,31 +6037,31 @@
       <c r="Y81" s="3"/>
       <c r="Z81" s="3"/>
     </row>
-    <row r="82" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A82" s="40" t="s">
-        <v>506</v>
-      </c>
-      <c r="B82" s="17" t="s">
-        <v>507</v>
+    <row r="82" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A82" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="B82" s="16" t="s">
+        <v>182</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>191</v>
+        <v>596</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>494</v>
+        <v>210</v>
       </c>
       <c r="E82" s="3"/>
-      <c r="F82" s="3" t="s">
-        <v>548</v>
+      <c r="F82" s="5" t="s">
+        <v>358</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>508</v>
+        <v>183</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>509</v>
+        <v>459</v>
       </c>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
@@ -5907,33 +6081,31 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
     </row>
-    <row r="83" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A83" s="40" t="s">
-        <v>510</v>
-      </c>
-      <c r="B83" s="17" t="s">
-        <v>511</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>191</v>
+    <row r="83" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A83" s="57" t="s">
+        <v>316</v>
+      </c>
+      <c r="B83" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>596</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="H83" s="18" t="s">
-        <v>513</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>514</v>
+      <c r="E83" s="12"/>
+      <c r="F83" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="G83" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="H83" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="I83" s="12" t="s">
+        <v>458</v>
       </c>
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
@@ -5953,31 +6125,31 @@
       <c r="Y83" s="3"/>
       <c r="Z83" s="3"/>
     </row>
-    <row r="84" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A84" s="41" t="s">
-        <v>253</v>
-      </c>
-      <c r="B84" s="26" t="s">
-        <v>272</v>
-      </c>
-      <c r="C84" s="28" t="s">
-        <v>273</v>
+    <row r="84" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A84" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B84" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>185</v>
       </c>
       <c r="D84" s="13" t="s">
         <v>210</v>
       </c>
       <c r="E84" s="3"/>
-      <c r="F84" s="18" t="s">
-        <v>557</v>
+      <c r="F84" s="5" t="s">
+        <v>354</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>543</v>
+        <v>186</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>286</v>
+        <v>187</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
@@ -5997,33 +6169,31 @@
       <c r="Y84" s="3"/>
       <c r="Z84" s="3"/>
     </row>
-    <row r="85" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A85" s="37" t="s">
-        <v>323</v>
-      </c>
-      <c r="B85" s="16" t="s">
-        <v>195</v>
+    <row r="85" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B85" s="17" t="s">
+        <v>188</v>
       </c>
       <c r="C85" s="29" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="E85" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>362</v>
+        <v>210</v>
+      </c>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3" t="s">
+        <v>359</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>400</v>
+        <v>538</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="J85" s="3"/>
       <c r="K85" s="3"/>
@@ -6043,33 +6213,33 @@
       <c r="Y85" s="3"/>
       <c r="Z85" s="3"/>
     </row>
-    <row r="86" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A86" s="37" t="s">
-        <v>322</v>
-      </c>
-      <c r="B86" s="16" t="s">
-        <v>198</v>
+    <row r="86" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A86" s="40" t="s">
+        <v>508</v>
+      </c>
+      <c r="B86" s="63" t="s">
+        <v>509</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D86" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="E86" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>363</v>
+      <c r="E86" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>546</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>199</v>
+        <v>540</v>
+      </c>
+      <c r="H86" s="18" t="s">
+        <v>511</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>469</v>
+        <v>512</v>
       </c>
       <c r="J86" s="3"/>
       <c r="K86" s="3"/>
@@ -6090,30 +6260,32 @@
       <c r="Z86" s="3"/>
     </row>
     <row r="87" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A87" s="4" t="s">
-        <v>200</v>
+      <c r="A87" s="36" t="s">
+        <v>318</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="C87" s="29" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D87" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="E87" s="3"/>
+      <c r="E87" s="4" t="s">
+        <v>317</v>
+      </c>
       <c r="F87" s="5" t="s">
-        <v>335</v>
+        <v>551</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>203</v>
+        <v>543</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="I87" s="48" t="s">
-        <v>467</v>
+        <v>194</v>
+      </c>
+      <c r="I87" s="46" t="s">
+        <v>462</v>
       </c>
       <c r="J87" s="3"/>
       <c r="K87" s="3"/>
@@ -6133,31 +6305,31 @@
       <c r="Y87" s="3"/>
       <c r="Z87" s="3"/>
     </row>
-    <row r="88" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A88" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="B88" s="14" t="s">
-        <v>205</v>
+    <row r="88" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A88" s="40" t="s">
+        <v>504</v>
+      </c>
+      <c r="B88" s="13" t="s">
+        <v>505</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>210</v>
+        <v>492</v>
       </c>
       <c r="E88" s="3"/>
-      <c r="F88" s="5" t="s">
-        <v>548</v>
+      <c r="F88" s="3" t="s">
+        <v>546</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>402</v>
+        <v>544</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>207</v>
+        <v>506</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>208</v>
+        <v>507</v>
       </c>
       <c r="J88" s="3"/>
       <c r="K88" s="3"/>
@@ -6177,33 +6349,31 @@
       <c r="Y88" s="3"/>
       <c r="Z88" s="3"/>
     </row>
-    <row r="89" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A89" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="B89" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="C89" t="s">
-        <v>268</v>
+    <row r="89" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A89" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B89" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="C89" s="64" t="s">
+        <v>191</v>
       </c>
       <c r="D89" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="F89" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="G89" s="18" t="s">
-        <v>398</v>
+      <c r="E89" s="3"/>
+      <c r="F89" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>539</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>283</v>
+        <v>192</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>468</v>
+        <v>193</v>
       </c>
       <c r="J89" s="3"/>
       <c r="K89" s="3"/>
@@ -6223,72 +6393,124 @@
       <c r="Y89" s="3"/>
       <c r="Z89" s="3"/>
     </row>
-    <row r="90" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A90" s="3"/>
-      <c r="B90" s="3"/>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3"/>
+    <row r="90" spans="1:26" s="25" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A90" s="40" t="s">
+        <v>252</v>
+      </c>
+      <c r="B90" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="C90" s="28" t="s">
+        <v>272</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>210</v>
+      </c>
       <c r="E90" s="3"/>
-      <c r="F90" s="3"/>
-      <c r="G90" s="3"/>
-      <c r="H90" s="3"/>
-      <c r="I90" s="3"/>
-      <c r="J90" s="3"/>
-      <c r="K90" s="3"/>
-      <c r="L90" s="3"/>
-      <c r="M90" s="3"/>
-      <c r="N90" s="3"/>
-      <c r="O90" s="3"/>
-      <c r="P90" s="3"/>
-      <c r="Q90" s="3"/>
-      <c r="R90" s="3"/>
-      <c r="S90" s="3"/>
-      <c r="T90" s="3"/>
-      <c r="U90" s="3"/>
-      <c r="V90" s="3"/>
-      <c r="W90" s="3"/>
-      <c r="X90" s="3"/>
-      <c r="Y90" s="3"/>
-      <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A91" s="3"/>
-      <c r="B91" s="3"/>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
-      <c r="I91" s="3"/>
-      <c r="J91" s="3"/>
-      <c r="K91" s="3"/>
-      <c r="L91" s="3"/>
-      <c r="M91" s="3"/>
-      <c r="N91" s="3"/>
-      <c r="O91" s="3"/>
-      <c r="P91" s="3"/>
-      <c r="Q91" s="3"/>
-      <c r="R91" s="3"/>
-      <c r="S91" s="3"/>
-      <c r="T91" s="3"/>
-      <c r="U91" s="3"/>
-      <c r="V91" s="3"/>
-      <c r="W91" s="3"/>
-      <c r="X91" s="3"/>
-      <c r="Y91" s="3"/>
-      <c r="Z91" s="3"/>
-    </row>
-    <row r="92" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A92" s="3"/>
-      <c r="B92" s="3"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
-      <c r="I92" s="3"/>
+      <c r="F90" s="18" t="s">
+        <v>555</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="J90" s="55"/>
+      <c r="K90" s="55"/>
+      <c r="L90" s="55"/>
+      <c r="M90" s="55"/>
+      <c r="N90" s="55"/>
+      <c r="O90" s="55"/>
+      <c r="P90" s="55"/>
+      <c r="Q90" s="55"/>
+      <c r="R90" s="55"/>
+      <c r="S90" s="55"/>
+      <c r="T90" s="55"/>
+      <c r="U90" s="55"/>
+      <c r="V90" s="55"/>
+      <c r="W90" s="55"/>
+      <c r="X90" s="55"/>
+      <c r="Y90" s="55"/>
+      <c r="Z90" s="55"/>
+    </row>
+    <row r="91" spans="1:26" s="25" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A91" s="36" t="s">
+        <v>321</v>
+      </c>
+      <c r="B91" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="E91" s="18" t="s">
+        <v>319</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="J91" s="55"/>
+      <c r="K91" s="55"/>
+      <c r="L91" s="55"/>
+      <c r="M91" s="55"/>
+      <c r="N91" s="55"/>
+      <c r="O91" s="55"/>
+      <c r="P91" s="55"/>
+      <c r="Q91" s="55"/>
+      <c r="R91" s="55"/>
+      <c r="S91" s="55"/>
+      <c r="T91" s="55"/>
+      <c r="U91" s="55"/>
+      <c r="V91" s="55"/>
+      <c r="W91" s="55"/>
+      <c r="X91" s="55"/>
+      <c r="Y91" s="55"/>
+      <c r="Z91" s="55"/>
+    </row>
+    <row r="92" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A92" s="36" t="s">
+        <v>320</v>
+      </c>
+      <c r="B92" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D92" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="E92" s="18" t="s">
+        <v>322</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>467</v>
+      </c>
       <c r="J92" s="3"/>
       <c r="K92" s="3"/>
       <c r="L92" s="3"/>
@@ -6307,16 +6529,32 @@
       <c r="Y92" s="3"/>
       <c r="Z92" s="3"/>
     </row>
-    <row r="93" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A93" s="3"/>
-      <c r="B93" s="3"/>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3"/>
+    <row r="93" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A93" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B93" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D93" s="13" t="s">
+        <v>210</v>
+      </c>
       <c r="E93" s="3"/>
-      <c r="F93" s="3"/>
-      <c r="G93" s="3"/>
-      <c r="H93" s="3"/>
-      <c r="I93" s="3"/>
+      <c r="F93" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>465</v>
+      </c>
       <c r="J93" s="3"/>
       <c r="K93" s="3"/>
       <c r="L93" s="3"/>
@@ -6336,15 +6574,29 @@
       <c r="Z93" s="3"/>
     </row>
     <row r="94" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A94" s="3"/>
-      <c r="B94" s="3"/>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3"/>
-      <c r="E94" s="3"/>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3"/>
-      <c r="H94" s="3"/>
-      <c r="I94" s="3"/>
+      <c r="A94" s="55" t="s">
+        <v>587</v>
+      </c>
+      <c r="B94" s="55" t="s">
+        <v>602</v>
+      </c>
+      <c r="C94" s="55" t="s">
+        <v>601</v>
+      </c>
+      <c r="D94" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="E94" s="55"/>
+      <c r="F94" s="55" t="s">
+        <v>610</v>
+      </c>
+      <c r="G94" s="60" t="s">
+        <v>633</v>
+      </c>
+      <c r="H94" s="56"/>
+      <c r="I94" s="61" t="s">
+        <v>634</v>
+      </c>
       <c r="J94" s="3"/>
       <c r="K94" s="3"/>
       <c r="L94" s="3"/>
@@ -6363,16 +6615,32 @@
       <c r="Y94" s="3"/>
       <c r="Z94" s="3"/>
     </row>
-    <row r="95" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A95" s="3"/>
-      <c r="B95" s="3"/>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
+    <row r="95" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A95" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B95" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>210</v>
+      </c>
       <c r="E95" s="3"/>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
-      <c r="I95" s="3"/>
+      <c r="F95" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>208</v>
+      </c>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
@@ -6391,44 +6659,74 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
     </row>
-    <row r="96" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A96" s="3"/>
-      <c r="B96" s="3"/>
-      <c r="C96" s="3"/>
-      <c r="D96" s="3"/>
+    <row r="96" spans="1:26" s="25" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="E96" s="3"/>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3"/>
-      <c r="H96" s="3"/>
-      <c r="I96" s="3"/>
-      <c r="J96" s="3"/>
-      <c r="K96" s="3"/>
-      <c r="L96" s="3"/>
-      <c r="M96" s="3"/>
-      <c r="N96" s="3"/>
-      <c r="O96" s="3"/>
-      <c r="P96" s="3"/>
-      <c r="Q96" s="3"/>
-      <c r="R96" s="3"/>
-      <c r="S96" s="3"/>
-      <c r="T96" s="3"/>
-      <c r="U96" s="3"/>
-      <c r="V96" s="3"/>
-      <c r="W96" s="3"/>
-      <c r="X96" s="3"/>
-      <c r="Y96" s="3"/>
-      <c r="Z96" s="3"/>
+      <c r="F96" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="G96" s="29" t="s">
+        <v>629</v>
+      </c>
+      <c r="H96" s="56"/>
+      <c r="I96" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="J96" s="55"/>
+      <c r="K96" s="55"/>
+      <c r="L96" s="55"/>
+      <c r="M96" s="55"/>
+      <c r="N96" s="55"/>
+      <c r="O96" s="55"/>
+      <c r="P96" s="55"/>
+      <c r="Q96" s="55"/>
+      <c r="R96" s="55"/>
+      <c r="S96" s="55"/>
+      <c r="T96" s="55"/>
+      <c r="U96" s="55"/>
+      <c r="V96" s="55"/>
+      <c r="W96" s="55"/>
+      <c r="X96" s="55"/>
+      <c r="Y96" s="55"/>
+      <c r="Z96" s="55"/>
     </row>
     <row r="97" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A97" s="3"/>
-      <c r="B97" s="3"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
-      <c r="I97" s="3"/>
+      <c r="A97" s="55" t="s">
+        <v>582</v>
+      </c>
+      <c r="B97" s="55" t="s">
+        <v>595</v>
+      </c>
+      <c r="C97" s="55" t="s">
+        <v>594</v>
+      </c>
+      <c r="D97" s="55" t="s">
+        <v>210</v>
+      </c>
+      <c r="E97" s="55"/>
+      <c r="F97" s="55" t="s">
+        <v>606</v>
+      </c>
+      <c r="G97" s="55" t="s">
+        <v>619</v>
+      </c>
+      <c r="H97" s="55" t="s">
+        <v>618</v>
+      </c>
+      <c r="I97" s="55" t="s">
+        <v>620</v>
+      </c>
       <c r="J97" s="3"/>
       <c r="K97" s="3"/>
       <c r="L97" s="3"/>
@@ -6448,15 +6746,33 @@
       <c r="Z97" s="3"/>
     </row>
     <row r="98" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A98" s="3"/>
-      <c r="B98" s="3"/>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="3"/>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3"/>
-      <c r="H98" s="3"/>
-      <c r="I98" s="3"/>
+      <c r="A98" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B98" s="50" t="s">
+        <v>265</v>
+      </c>
+      <c r="C98" s="28" t="s">
+        <v>267</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="F98" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G98" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>466</v>
+      </c>
       <c r="J98" s="3"/>
       <c r="K98" s="3"/>
       <c r="L98" s="3"/>
@@ -31705,8 +32021,9 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I999">
-    <sortCondition ref="C1:C999"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I98">
+    <sortCondition ref="C2:C98"/>
+    <sortCondition ref="A2:A98"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
